--- a/artfynd/A 59408-2020 artfynd.xlsx
+++ b/artfynd/A 59408-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>117515308</v>
       </c>
       <c r="B2" t="n">
-        <v>57990</v>
+        <v>57991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>117515306</v>
       </c>
       <c r="B3" t="n">
-        <v>57789</v>
+        <v>57790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -920,6 +920,246 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118113186</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57204</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hygge strax S om Blacke, Lövånger, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>808620</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7153473</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niklas Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niklas Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118113181</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hygge strax S om Blacke, Lövånger, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>808620</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7153473</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niklas Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59408-2020 artfynd.xlsx
+++ b/artfynd/A 59408-2020 artfynd.xlsx
@@ -1044,11 +1044,11 @@
         <v>118113181</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>57586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
